--- a/public/templates/mau_so_du_dau_ky.xlsx
+++ b/public/templates/mau_so_du_dau_ky.xlsx
@@ -517,7 +517,7 @@
         <v>NCC_FOOD</v>
       </c>
       <c r="E5" t="str">
-        <v>NCC Thuc pham Sach</v>
+        <v>NCC Nguyen lieu</v>
       </c>
       <c r="F5" t="str">
         <v/>

--- a/public/templates/mau_so_du_dau_ky.xlsx
+++ b/public/templates/mau_so_du_dau_ky.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:N9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,9 +419,27 @@
         <v>Nguon tien</v>
       </c>
       <c r="G1" t="str">
+        <v>Kho</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Phong ban</v>
+      </c>
+      <c r="I1" t="str">
+        <v>So luong</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Don gia</v>
+      </c>
+      <c r="K1" t="str">
+        <v>So ky phan bo</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Ky bat dau phan bo</v>
+      </c>
+      <c r="M1" t="str">
         <v>So tien</v>
       </c>
-      <c r="H1" t="str">
+      <c r="N1" t="str">
         <v>Ghi chu</v>
       </c>
     </row>
@@ -444,10 +462,28 @@
       <c r="F2" t="str">
         <v>VCB_HCM</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2">
         <v>2500000000</v>
       </c>
-      <c r="H2" t="str">
+      <c r="N2" t="str">
         <v>So du ngan hang dau ky</v>
       </c>
     </row>
@@ -470,10 +506,28 @@
       <c r="F3" t="str">
         <v>TM_HCM</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3">
         <v>120000000</v>
       </c>
-      <c r="H3" t="str">
+      <c r="N3" t="str">
         <v>Quy tien mat dau ky</v>
       </c>
     </row>
@@ -496,10 +550,28 @@
       <c r="F4" t="str">
         <v/>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4">
         <v>50000000</v>
       </c>
-      <c r="H4" t="str">
+      <c r="N4" t="str">
         <v>Phai thu dau ky</v>
       </c>
     </row>
@@ -522,10 +594,28 @@
       <c r="F5" t="str">
         <v/>
       </c>
-      <c r="G5">
-        <v>-18500000</v>
+      <c r="G5" t="str">
+        <v/>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5">
+        <v>18500000</v>
+      </c>
+      <c r="N5" t="str">
         <v>Phai tra dau ky</v>
       </c>
     </row>
@@ -548,16 +638,166 @@
       <c r="F6" t="str">
         <v>VCB_HCM</v>
       </c>
-      <c r="G6">
-        <v>50000000</v>
+      <c r="G6" t="str">
+        <v/>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6">
+        <v>7000000</v>
+      </c>
+      <c r="N6" t="str">
         <v>Tien coc dang giu</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="B7" t="str">
+        <v>HCM</v>
+      </c>
+      <c r="C7" t="str">
+        <v>INVENTORY</v>
+      </c>
+      <c r="D7" t="str">
+        <v>NL001</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Nguyen lieu mau</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>KHO_HCM</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7">
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>32000</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7">
+        <v>1600000</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Ton kho dau ky</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>HCM</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ASSET</v>
+      </c>
+      <c r="D8" t="str">
+        <v>TS001</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Thiet bi dau ky</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>STORE</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>18000000</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8">
+        <v>18000000</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Tai san/CCDC dau ky</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="B9" t="str">
+        <v>HCM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>PREPAID_EXPENSE</v>
+      </c>
+      <c r="D9" t="str">
+        <v>PB001</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Chi phi phan bo dau ky</v>
+      </c>
+      <c r="F9" t="str">
+        <v>OPEX_RENT</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9">
+        <v>12</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-07</v>
+      </c>
+      <c r="M9">
+        <v>120000000</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Chi phi phan bo dau ky</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/mau_so_du_dau_ky.xlsx
+++ b/public/templates/mau_so_du_dau_ky.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,9 +437,12 @@
         <v>Ky bat dau phan bo</v>
       </c>
       <c r="M1" t="str">
+        <v>Hang muc P&amp;L</v>
+      </c>
+      <c r="N1" t="str">
         <v>So tien</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Ghi chu</v>
       </c>
     </row>
@@ -480,10 +483,13 @@
       <c r="L2" t="str">
         <v/>
       </c>
-      <c r="M2">
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2">
         <v>2500000000</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>So du ngan hang dau ky</v>
       </c>
     </row>
@@ -524,10 +530,13 @@
       <c r="L3" t="str">
         <v/>
       </c>
-      <c r="M3">
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3">
         <v>120000000</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>Quy tien mat dau ky</v>
       </c>
     </row>
@@ -568,10 +577,13 @@
       <c r="L4" t="str">
         <v/>
       </c>
-      <c r="M4">
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4">
         <v>50000000</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>Phai thu dau ky</v>
       </c>
     </row>
@@ -612,10 +624,13 @@
       <c r="L5" t="str">
         <v/>
       </c>
-      <c r="M5">
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5">
         <v>18500000</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>Phai tra dau ky</v>
       </c>
     </row>
@@ -656,10 +671,13 @@
       <c r="L6" t="str">
         <v/>
       </c>
-      <c r="M6">
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6">
         <v>7000000</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>Tien coc dang giu</v>
       </c>
     </row>
@@ -700,10 +718,13 @@
       <c r="L7" t="str">
         <v/>
       </c>
-      <c r="M7">
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7">
         <v>1600000</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>Ton kho dau ky</v>
       </c>
     </row>
@@ -744,10 +765,13 @@
       <c r="L8" t="str">
         <v/>
       </c>
-      <c r="M8">
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8">
         <v>18000000</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>Tai san/CCDC dau ky</v>
       </c>
     </row>
@@ -788,16 +812,19 @@
       <c r="L9" t="str">
         <v>2026-07</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="str">
+        <v>PNL_THUE_MB</v>
+      </c>
+      <c r="N9">
         <v>120000000</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>Chi phi phan bo dau ky</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O9"/>
   </ignoredErrors>
 </worksheet>
 </file>